--- a/data_analysis/results_data_analysis/Indicators_PyPSAEurSmall.xlsx
+++ b/data_analysis/results_data_analysis/Indicators_PyPSAEurSmall.xlsx
@@ -675,16 +675,16 @@
         <v>16</v>
       </c>
       <c r="B14">
-        <v>52.85907006263733</v>
+        <v>56.87339615821838</v>
       </c>
       <c r="C14">
-        <v>41.24168086051941</v>
+        <v>41.23347163200378</v>
       </c>
       <c r="D14">
-        <v>54.53494358062744</v>
+        <v>56.02601027488708</v>
       </c>
       <c r="E14">
-        <v>11.8998715877533</v>
+        <v>12.22037243843079</v>
       </c>
     </row>
     <row r="15" spans="1:5">
